--- a/data/trans_dic/IP31KM15_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM15_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>54,01%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>28,34; 57,15</t>
+          <t>42,67; 66,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>40,86; 63,84</t>
+          <t>40,56; 65,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37,62; 58,63</t>
+          <t>45,69; 63,18</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>57,1%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>45,57; 61,15</t>
+          <t>50,34; 59,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>49,18; 58,87</t>
+          <t>55,27; 63,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>49,16; 58,71</t>
+          <t>53,97; 60,19</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>56,53%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>50,1; 64,05</t>
+          <t>48,79; 62,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>49,84; 63,42</t>
+          <t>49,82; 63,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51,58; 61,3</t>
+          <t>51,77; 61,34</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>56,73%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>47,56; 59,4</t>
+          <t>51,94; 59,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>50,79; 57,96</t>
+          <t>54,79; 61,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51,1; 57,56</t>
+          <t>54,25; 59,2</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23184</t>
+          <t>29612</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30575</t>
+          <t>24197</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53758</t>
+          <t>53809</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>15218; 30689</t>
+          <t>22921; 35733</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23842; 37245</t>
+          <t>18620; 29840</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42146; 65686</t>
+          <t>45515; 62937</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>374</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>335</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>253817</t>
+          <t>257200</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>273215</t>
+          <t>251644</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>527032</t>
+          <t>508844</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>205904; 276295</t>
+          <t>234787; 277656</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>248485; 297465</t>
+          <t>234710; 269605</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>470498; 561866</t>
+          <t>480956; 536364</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>128</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>83442</t>
+          <t>93295</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>101804</t>
+          <t>84109</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>185245</t>
+          <t>177403</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>73236; 93632</t>
+          <t>81320; 104215</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>90272; 114869</t>
+          <t>73307; 93842</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>168848; 200647</t>
+          <t>162476; 192493</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>505</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>534</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>505</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>360443</t>
+          <t>380108</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>405593</t>
+          <t>359949</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>766036</t>
+          <t>740057</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>309938; 387122</t>
+          <t>356711; 407480</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>378260; 431631</t>
+          <t>338435; 381826</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>713617; 803824</t>
+          <t>707705; 772332</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM15_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM15_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que toman 2 yogures y/o 40 g de queso cada día (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>55,13%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>52,71%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>54,01%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>42,67; 66,52</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>40,56; 65,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>45,69; 63,18</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>55,14%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>59,26%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57,1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>50,34; 59,53</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>55,27; 63,49</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>53,97; 60,19</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>55,97%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>57,16%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>56,53%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>48,79; 62,52</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>49,82; 63,78</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>51,77; 61,34</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>55,34%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>58,27%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>56,73%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>51,94; 59,33</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>54,79; 61,81</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>54,25; 59,2</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.5512868333965557</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.5271121775181079</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.5401471244391874</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>29612</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>24197</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>53809</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.426722857835206</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.4056265349037443</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.4568879261701941</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>22921; 35733</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>18620; 29840</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>45515; 62937</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.6652421865667689</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.6500285936773894</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.6317706218677147</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>709</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.5514309783963809</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.5925683984874677</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.5710358277243544</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>257200</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>251644</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>508844</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.5033773876372202</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.5526943171209145</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.5397389100407088</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>234787; 277656</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>234710; 269605</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>480956; 536364</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.5952872401862973</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.6348642179893762</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.6019186188724042</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.5597055649567524</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.5716237379936907</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.5652935037781047</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>93295</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>84109</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>177403</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.4878628311109628</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.4982113164995609</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.5177273345084755</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>81320; 104215</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>73307; 93842</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>162476; 192493</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.6252202333060125</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.6377737448342928</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.6133776925943544</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>505</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>534</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1039</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.5534278688418931</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.5827150106241451</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.5672956400312481</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>380108</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>359949</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>740057</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.5193635760153495</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.5478853049308617</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.5424959043607993</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>356711; 407480</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>338435; 381826</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>707705; 772332</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.5932814819740828</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.6181302037097802</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.5920366005286551</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que toman 2 yogures y/o 40 g de queso cada día (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>29612</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>24197</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>53809</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>22921</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>18620</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>45515</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>35733</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>29840</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>62937</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>335</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>374</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>257200</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>251644</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>508844</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>234787</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>234710</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>480956</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>277656</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>269605</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>536364</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>132</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>128</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>93295</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>84109</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>177403</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>81320</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>73307</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>162476</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>104215</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>93842</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>192493</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>505</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>534</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>380108</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>359949</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>740057</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>356711</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>338435</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>707705</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>407480</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>381826</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>772332</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>